--- a/output/2026-08-31_17_Italia_Emilia_Romagna_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-08-31_17_Italia_Emilia_Romagna_Componentistica_Ventilazione_industriale.xlsx
@@ -498,10 +498,9 @@
           <t>348 5709040</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Confermata da fonti pubbliche (sito aziendale, reportaziende.it). ATTENZIONE: indirizzo fornito (Via Caduti della Libertà 48/B) non coincide con quello risultante da fonte esterna (Via Dante Alighieri 3/c, Zola Predosa) - da verificare quale sia attuale.</t>
+          <t>Confermata da fonti pubbliche (sito aziendale, reportaziende.it). ATTENZIONE: indirizzo fornito (Via Caduti della Libertà 48/B) non coincide con quello risultante da fonte esterna (Via Dante Alighieri 3/c, Zola Predosa) - da verificare quale sia attuale. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Impiantistica_aspirazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -615,11 +614,9 @@
           <t>Impianti/componenti aspirazione e filtrazione aria industriale, componenti ATEX</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Confermata: leader da 48 anni in aspirazione/filtrazione fumi e polveri, componenti certificati ATEX. Telefono/email non reperiti nei risultati di ricerca.</t>
+          <t>Confermata: leader da 48 anni in aspirazione/filtrazione fumi e polveri, componenti certificati ATEX. Telefono/email non reperiti nei risultati di ricerca. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -654,10 +651,9 @@
           <t>0536 071051</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Confermata: oltre 35 anni di esperienza, vendita ricambi/accessori per aspirazione industriale, Sassuolo (MO).</t>
+          <t>Confermata: oltre 35 anni di esperienza, vendita ricambi/accessori per aspirazione industriale, Sassuolo (MO). [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -741,7 +737,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Confermata: rivenditore/centro assistenza FAR, ricambi elettropompe e ventilatori industriali, Modena.</t>
+          <t>Confermata: rivenditore/centro assistenza FAR, ricambi elettropompe e ventilatori industriali, Modena. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -860,7 +856,6 @@
           <t>0522 517829</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>Confermata: dal 1976, produttore ventilatori assiali (250-2000mm) e centrifughi, Reggio Emilia.</t>
@@ -893,8 +888,6 @@
           <t>Filtri per impianti di aspirazione centralizzati, filtri a maniche/cartucce</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>Confermata: Rio Saliceto (RE), produttore filtri a maniche/cartucce per aspirazione centralizzata polveri industriali. Telefono/email non reperiti.</t>
@@ -1016,7 +1009,6 @@
           <t>0525 39441</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Confermata: dal 1979, Solignano/Rubbiano (PR), commercializza bocchette, serrande, griglie, filtri, ventilatori, UTA. Telefono reperito da fonte directory, non presente nel dato grezzo - da confermare.</t>
@@ -1054,7 +1046,6 @@
           <t>0523 613655</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Confermata: oltre 30 anni di esperienza, certificazione ISO 9001:2015, produzione condotte aria/filtri, Piacenza.</t>
@@ -1092,7 +1083,6 @@
           <t>0523 949142</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Confermata: Alseno (PC), commercializzazione componenti/ricambi per compressori, soffianti e aspiratori.</t>
@@ -1130,10 +1120,9 @@
           <t>+39 0523 524066</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Confermata: oltre 40 anni, produttore filtri a cartuccia e sistemi di aspirazione/filtrazione per lavorazione lamiera, Podenzano (PC). Focus principale su macchine per lavorazione lamiera, aspirazione/filtrazione come linea correlata.</t>
+          <t>Confermata: oltre 40 anni, produttore filtri a cartuccia e sistemi di aspirazione/filtrazione per lavorazione lamiera, Podenzano (PC). Focus principale su macchine per lavorazione lamiera, aspirazione/filtrazione come linea correlata. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1175,7 +1164,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Confermata: dal 1979, progettazione impianti aeraulici per ventilazione/climatizzazione industriale e civile, Ferrara.</t>
+          <t>Confermata: dal 1979, progettazione impianti aeraulici per ventilazione/climatizzazione industriale e civile, Ferrara. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1190,7 +1179,6 @@
           <t>Fanti Aurelio - Impianti Aspirazione Depurazione</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>Ravenna</t>
@@ -1206,7 +1194,6 @@
           <t>0544 71645</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>Confermata: ditta individuale (P.IVA 00321210395), Cervia (RA), cappe per cucine/laboratori e impianti aspirazione/depurazione. Nessun sito web reperito.</t>
@@ -1244,10 +1231,9 @@
           <t>0543 795959</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Confermata: dal 2003 (esperienza dal 1993), certificazione ISO 9001:2015, impianti aeraulici/aspirazione industriale, Forlì.</t>
+          <t>Confermata: dal 2003 (esperienza dal 1993), certificazione ISO 9001:2015, impianti aeraulici/aspirazione industriale, Forlì. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1289,7 +1275,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Confermata: oltre 30 anni, progettazione/realizzazione impianti filtrazione aria industriale e fornitura ricambi, Forlì.</t>
+          <t>Confermata: oltre 30 anni, progettazione/realizzazione impianti filtrazione aria industriale e fornitura ricambi, Forlì. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1366,10 +1352,9 @@
           <t>0541 827127</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Confermata: produzione/installazione condotte e componenti ventilazione/aspirazione in acciaio inox/zincato/rame/alluminio, San Giovanni in Marignano (RN); attiva su tutta l'Emilia Romagna e Marche.</t>
+          <t>Confermata: produzione/installazione condotte e componenti ventilazione/aspirazione in acciaio inox/zincato/rame/alluminio, San Giovanni in Marignano (RN); attiva su tutta l'Emilia Romagna e Marche. [DUPLICATO — vedi anche: 2026-08-31_16_Italia_Emilia_Romagna_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
